--- a/product_surveys/027_new_product_evaluation--product_surveys.xlsx
+++ b/product_surveys/027_new_product_evaluation--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="39" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -717,7 +717,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Age Group Other</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>product_launching_as</t>
+          <t>product_launching_as_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Product launching as</t>
+          <t>Product Launching As 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>product_name</t>
+          <t>product_name_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>product_name</t>
+          <t>Product Name 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>product_description</t>
+          <t>product_description_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>product_description</t>
+          <t>Product Description 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1084,12 +1084,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>feedback_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Feedback 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>target_audience</t>
+          <t>target_audience_2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>target_audience</t>
+          <t>Target Audience 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1136,7 +1136,7 @@
   <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1603,7 +1603,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>product_launching_as_choices</t>
+          <t>product_launching_as_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1620,7 +1620,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>product_launching_as_choices</t>
+          <t>product_launching_as_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1637,7 +1637,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>target_audience_choices</t>
+          <t>target_audience_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1654,7 +1654,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>target_audience_choices</t>
+          <t>target_audience_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1671,7 +1671,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>target_audience_choices</t>
+          <t>target_audience_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1688,7 +1688,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>target_audience_choices</t>
+          <t>target_audience_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
